--- a/agrra_monitoring/data_raw/ATG_NPA_2025/Raw/Metadata.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NPA_2025/Raw/Metadata.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\AGRRA\Sent Product Files\products\Raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NDNP2025\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204E176E-97D4-4259-826D-1CF48F444E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF6743-AB22-4B7D-8A34-A82F0397E42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="8" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="9" r:id="rId1"/>
     <sheet name="Batch" sheetId="1" r:id="rId2"/>
     <sheet name="Survey" sheetId="2" r:id="rId3"/>
     <sheet name="Transect" sheetId="3" r:id="rId4"/>
@@ -22,7 +22,7 @@
     <sheet name="CoralTaxonomy" sheetId="6" r:id="rId7"/>
     <sheet name="FishTaxonomy" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -2483,48 +2483,39 @@
     <t>Diadema Predator</t>
   </si>
   <si>
-    <t>Created: 2025 Aug 8</t>
-  </si>
-  <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
+    <t>Created: 2026 May 29</t>
+  </si>
+  <si>
+    <t>AGRRA Terms of Data Service</t>
+  </si>
+  <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="13"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Ruleo Camacho. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
-</t>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
     </r>
     <r>
       <rPr>
@@ -2535,17 +2526,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
     </r>
     <r>
       <rPr>
@@ -2556,17 +2546,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2577,17 +2566,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
     </r>
     <r>
       <rPr>
@@ -2598,17 +2585,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -2619,16 +2604,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2639,19 +2624,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
-</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2661,27 +2643,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
-    </r>
-  </si>
-  <si>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2691,18 +2662,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
-    </r>
-  </si>
-  <si>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2712,6 +2682,601 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A. Guidance for Original Data Contributors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B. Guidance for Third-Party Data Users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">How to cite original data contributors: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Direct contact and collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Integrity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No Warranty:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Metadata:</t>
     </r>
     <r>
@@ -2724,23 +3289,30 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-      </rPr>
-      <t>©</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format of Data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -2753,11 +3325,18 @@
     <numFmt numFmtId="165" formatCode="0.0000&quot;° N&quot;;0.0000&quot;° S&quot;;0.0000&quot;°&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0000&quot;° E&quot;;0.0000&quot;° W&quot;;0.0000&quot;°&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2781,16 +3360,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2813,7 +3411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2827,6 +3425,66 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2840,7 +3498,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2963,11 +3636,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2994,114 +3668,105 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{BCE2149B-F709-42DF-914E-D5F48F48F924}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{BE7D758F-BD3F-4923-A4CF-BA8C00FADF44}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{B74F2201-14E8-4B2E-82DF-C757829A495A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -3114,61 +3779,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{800E13A0-BF54-41A0-922D-90DEA1720B39}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3457,1051 +4067,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72FD573E-B28A-46BF-BE0D-7EC5384AA291}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26E63D7-AFCD-40DC-8011-54D75AD61141}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="13" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="13"/>
+    <col min="2" max="2" width="11.26953125" style="13" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>399</v>
       </c>
       <c r="B1" s="12"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="12"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="18"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="21"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
         <v>401</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="24"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
         <v>402</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="17"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="27"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="30"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="30"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="30"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="30"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="30"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="30"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="30"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="30"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="30"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="30"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="30"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="30"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="30"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="30"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="30"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="30"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="30"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="30"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="30"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="30"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="30"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="30"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+      <c r="W33" s="30"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="30"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="30"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="30"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="30"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="30"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+      <c r="W39" s="30"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="30"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="30"/>
+      <c r="X41" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="21" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="30"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="30"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+      <c r="W44" s="30"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="28"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+      <c r="W45" s="30"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="30"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+      <c r="W47" s="30"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="30"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="30"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
+      <c r="S50" s="29"/>
+      <c r="T50" s="29"/>
+      <c r="U50" s="29"/>
+      <c r="V50" s="29"/>
+      <c r="W50" s="30"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
+      <c r="U51" s="29"/>
+      <c r="V51" s="29"/>
+      <c r="W51" s="30"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="30"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="29"/>
+      <c r="Q53" s="29"/>
+      <c r="R53" s="29"/>
+      <c r="S53" s="29"/>
+      <c r="T53" s="29"/>
+      <c r="U53" s="29"/>
+      <c r="V53" s="29"/>
+      <c r="W53" s="30"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
+      <c r="U54" s="29"/>
+      <c r="V54" s="29"/>
+      <c r="W54" s="30"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="28"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="30"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="29"/>
+      <c r="S56" s="29"/>
+      <c r="T56" s="29"/>
+      <c r="U56" s="29"/>
+      <c r="V56" s="29"/>
+      <c r="W56" s="30"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
+      <c r="V57" s="29"/>
+      <c r="W57" s="30"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="30"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="28"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="29"/>
+      <c r="T59" s="29"/>
+      <c r="U59" s="29"/>
+      <c r="V59" s="29"/>
+      <c r="W59" s="30"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
+      <c r="U60" s="29"/>
+      <c r="V60" s="29"/>
+      <c r="W60" s="30"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="30"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
+      <c r="P62" s="29"/>
+      <c r="Q62" s="29"/>
+      <c r="R62" s="29"/>
+      <c r="S62" s="29"/>
+      <c r="T62" s="29"/>
+      <c r="U62" s="29"/>
+      <c r="V62" s="29"/>
+      <c r="W62" s="30"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="31"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32"/>
+      <c r="N63" s="32"/>
+      <c r="O63" s="32"/>
+      <c r="P63" s="32"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
+      <c r="V63" s="32"/>
+      <c r="W63" s="33"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="34"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="35" t="s">
+        <v>407</v>
+      </c>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="37"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="38"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="39"/>
+      <c r="R66" s="39"/>
+      <c r="S66" s="39"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="39"/>
+      <c r="V66" s="39"/>
+      <c r="W66" s="40"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="41" t="s">
         <v>404</v>
       </c>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="23"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="29"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="29"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="29"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="28"/>
-      <c r="W21" s="29"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="29"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="29"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="29"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="29"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="29"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="29"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="29"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="29"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
-      <c r="V30" s="28"/>
-      <c r="W30" s="29"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="29"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="29"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="29"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="29"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="29"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="29"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="29"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="29"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="29"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="29"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="29"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="29"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="29"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="28"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="29"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="28"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="28"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="29"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="29"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="34"/>
-      <c r="T47" s="34"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="35"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
-        <v>405</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="37"/>
-      <c r="L48" s="37"/>
-      <c r="M48" s="37"/>
-      <c r="N48" s="37"/>
-      <c r="O48" s="37"/>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="37"/>
-      <c r="S48" s="37"/>
-      <c r="T48" s="37"/>
-      <c r="U48" s="37"/>
-      <c r="V48" s="37"/>
-      <c r="W48" s="38"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="40"/>
-      <c r="V49" s="40"/>
-      <c r="W49" s="41"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="43"/>
-      <c r="P50" s="43"/>
-      <c r="Q50" s="43"/>
-      <c r="R50" s="43"/>
-      <c r="S50" s="43"/>
-      <c r="T50" s="43"/>
-      <c r="U50" s="43"/>
-      <c r="V50" s="43"/>
-      <c r="W50" s="44"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="45" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="46"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="47"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="47"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="47"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="47"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="47"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="47"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="47"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="47"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="47"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="47"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="47"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="47"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="47"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="47"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="47"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="47"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42"/>
+      <c r="N67" s="42"/>
+      <c r="O67" s="42"/>
+      <c r="P67" s="42"/>
+      <c r="Q67" s="42"/>
+      <c r="R67" s="42"/>
+      <c r="S67" s="42"/>
+      <c r="T67" s="42"/>
+      <c r="U67" s="42"/>
+      <c r="V67" s="42"/>
+      <c r="W67" s="43"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="34"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="34"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -4518,7 +5678,7 @@
     <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -4559,7 +5719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>66</v>
       </c>
@@ -4609,7 +5769,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
@@ -4635,7 +5795,7 @@
     <col min="22" max="22" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -4703,7 +5863,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -4765,7 +5925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -4827,7 +5987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -4889,7 +6049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -4951,7 +6111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -5013,7 +6173,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -5075,7 +6235,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -5137,7 +6297,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -5199,7 +6359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -5261,7 +6421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -5323,7 +6483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -5385,7 +6545,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -5447,7 +6607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -5509,7 +6669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -5580,7 +6740,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H240"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -5592,7 +6752,7 @@
     <col min="8" max="8" width="94" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -5618,7 +6778,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3122</v>
       </c>
@@ -5641,7 +6801,7 @@
         <v>45763.416666666999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3131</v>
       </c>
@@ -5664,7 +6824,7 @@
         <v>45764.427083333001</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3132</v>
       </c>
@@ -5687,7 +6847,7 @@
         <v>45763.444444444001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3133</v>
       </c>
@@ -5710,7 +6870,7 @@
         <v>45763.402777777999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3324</v>
       </c>
@@ -5733,7 +6893,7 @@
         <v>45763.4375</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3325</v>
       </c>
@@ -5756,7 +6916,7 @@
         <v>45763.46875</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4315</v>
       </c>
@@ -5779,7 +6939,7 @@
         <v>45763.414583332997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4316</v>
       </c>
@@ -5802,7 +6962,7 @@
         <v>45763.418055556001</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4317</v>
       </c>
@@ -5825,7 +6985,7 @@
         <v>45763.421527778002</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4318</v>
       </c>
@@ -5848,7 +7008,7 @@
         <v>45763.425694443999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>4319</v>
       </c>
@@ -5871,7 +7031,7 @@
         <v>45763.429861110999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>4320</v>
       </c>
@@ -5894,7 +7054,7 @@
         <v>45763.433333333</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4321</v>
       </c>
@@ -5917,7 +7077,7 @@
         <v>45763.4375</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>4322</v>
       </c>
@@ -5940,7 +7100,7 @@
         <v>45763.441666667</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>4335</v>
       </c>
@@ -5963,7 +7123,7 @@
         <v>45763.416666666999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4336</v>
       </c>
@@ -5986,7 +7146,7 @@
         <v>45763.430555555999</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>4337</v>
       </c>
@@ -6009,7 +7169,7 @@
         <v>45763.4375</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>4338</v>
       </c>
@@ -6032,7 +7192,7 @@
         <v>45763.444444444001</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>3115</v>
       </c>
@@ -6055,7 +7215,7 @@
         <v>45762.489583333001</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>3116</v>
       </c>
@@ -6078,7 +7238,7 @@
         <v>45762.506944444001</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>3117</v>
       </c>
@@ -6101,7 +7261,7 @@
         <v>45762.540277777996</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>3320</v>
       </c>
@@ -6124,7 +7284,7 @@
         <v>45762.388888889</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>3321</v>
       </c>
@@ -6150,7 +7310,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>3323</v>
       </c>
@@ -6173,7 +7333,7 @@
         <v>45762.46875</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>4307</v>
       </c>
@@ -6196,7 +7356,7 @@
         <v>45762.490277778001</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>4308</v>
       </c>
@@ -6219,7 +7379,7 @@
         <v>45762.495138888997</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>4309</v>
       </c>
@@ -6242,7 +7402,7 @@
         <v>45762.499305555997</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>4310</v>
       </c>
@@ -6265,7 +7425,7 @@
         <v>45762.503472222001</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>4311</v>
       </c>
@@ -6288,7 +7448,7 @@
         <v>45762.508333332997</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4312</v>
       </c>
@@ -6311,7 +7471,7 @@
         <v>45762.513194444</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>4313</v>
       </c>
@@ -6334,7 +7494,7 @@
         <v>45762.518055556</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4314</v>
       </c>
@@ -6357,7 +7517,7 @@
         <v>45762.523611110999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>4327</v>
       </c>
@@ -6380,7 +7540,7 @@
         <v>45762.548611111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>4328</v>
       </c>
@@ -6403,7 +7563,7 @@
         <v>45762.552083333001</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4329</v>
       </c>
@@ -6426,7 +7586,7 @@
         <v>45762.559027777999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>4330</v>
       </c>
@@ -6449,7 +7609,7 @@
         <v>45762.569444444001</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3111</v>
       </c>
@@ -6472,7 +7632,7 @@
         <v>45762.427083333001</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>3112</v>
       </c>
@@ -6495,7 +7655,7 @@
         <v>45762.453472221998</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>3114</v>
       </c>
@@ -6518,7 +7678,7 @@
         <v>45762.469444444003</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>3311</v>
       </c>
@@ -6541,7 +7701,7 @@
         <v>45762.395833333001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>3314</v>
       </c>
@@ -6564,7 +7724,7 @@
         <v>45762.423611111</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>3315</v>
       </c>
@@ -6587,7 +7747,7 @@
         <v>45762.46875</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4299</v>
       </c>
@@ -6610,7 +7770,7 @@
         <v>45762.408333332998</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4300</v>
       </c>
@@ -6633,7 +7793,7 @@
         <v>45762.413888889001</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4301</v>
       </c>
@@ -6656,7 +7816,7 @@
         <v>45762.419444444</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4302</v>
       </c>
@@ -6679,7 +7839,7 @@
         <v>45762.425000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4303</v>
       </c>
@@ -6702,7 +7862,7 @@
         <v>45762.428472222004</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4304</v>
       </c>
@@ -6725,7 +7885,7 @@
         <v>45762.433333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>4305</v>
       </c>
@@ -6748,7 +7908,7 @@
         <v>45762.438194444003</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>4306</v>
       </c>
@@ -6771,7 +7931,7 @@
         <v>45762.443055556003</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>4331</v>
       </c>
@@ -6794,7 +7954,7 @@
         <v>45762.465277777999</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>4332</v>
       </c>
@@ -6817,7 +7977,7 @@
         <v>45762.555555555999</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>4333</v>
       </c>
@@ -6840,7 +8000,7 @@
         <v>45762.479166666999</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>4334</v>
       </c>
@@ -6863,7 +8023,7 @@
         <v>45762.458333333001</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>3118</v>
       </c>
@@ -6886,7 +8046,7 @@
         <v>45763.461805555999</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>3119</v>
       </c>
@@ -6909,7 +8069,7 @@
         <v>45763.475694444001</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>3120</v>
       </c>
@@ -6932,7 +8092,7 @@
         <v>45763.489583333001</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>3330</v>
       </c>
@@ -6955,7 +8115,7 @@
         <v>45763.399305555999</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>3331</v>
       </c>
@@ -6978,7 +8138,7 @@
         <v>45763.427083333001</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>3332</v>
       </c>
@@ -7004,7 +8164,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>4323</v>
       </c>
@@ -7027,7 +8187,7 @@
         <v>45763.472222222001</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>4324</v>
       </c>
@@ -7050,7 +8210,7 @@
         <v>45763.476388889001</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4325</v>
       </c>
@@ -7073,7 +8233,7 @@
         <v>45763.481944444</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4326</v>
       </c>
@@ -7096,7 +8256,7 @@
         <v>45763.486111111</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>4339</v>
       </c>
@@ -7119,7 +8279,7 @@
         <v>45763.5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>4340</v>
       </c>
@@ -7142,7 +8302,7 @@
         <v>45763.503472222001</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>4341</v>
       </c>
@@ -7165,7 +8325,7 @@
         <v>45763.434027777999</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>4342</v>
       </c>
@@ -7188,7 +8348,7 @@
         <v>45763.444444444001</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>4343</v>
       </c>
@@ -7211,7 +8371,7 @@
         <v>45763.524305555999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>4344</v>
       </c>
@@ -7234,7 +8394,7 @@
         <v>45763.527777777999</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>4345</v>
       </c>
@@ -7257,7 +8417,7 @@
         <v>45763.53125</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>4346</v>
       </c>
@@ -7280,7 +8440,7 @@
         <v>45763.545138889</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>3766</v>
       </c>
@@ -7303,7 +8463,7 @@
         <v>45849.549305556</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>3767</v>
       </c>
@@ -7326,7 +8486,7 @@
         <v>45849.565277777998</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>3768</v>
       </c>
@@ -7349,7 +8509,7 @@
         <v>45849.085416667003</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>3805</v>
       </c>
@@ -7372,7 +8532,7 @@
         <v>45758.557638888997</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>3809</v>
       </c>
@@ -7395,7 +8555,7 @@
         <v>45849.572916666999</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>3810</v>
       </c>
@@ -7418,7 +8578,7 @@
         <v>45849.586111110999</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>5117</v>
       </c>
@@ -7441,7 +8601,7 @@
         <v>45849.375</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>5118</v>
       </c>
@@ -7464,7 +8624,7 @@
         <v>45849.381944444001</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>5119</v>
       </c>
@@ -7487,7 +8647,7 @@
         <v>45849.384027777996</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>5120</v>
       </c>
@@ -7510,7 +8670,7 @@
         <v>45849.387499999997</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>5121</v>
       </c>
@@ -7533,7 +8693,7 @@
         <v>45849.392361111</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>5122</v>
       </c>
@@ -7556,7 +8716,7 @@
         <v>45849.395833333001</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>5123</v>
       </c>
@@ -7579,7 +8739,7 @@
         <v>45849.399305555999</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>5124</v>
       </c>
@@ -7602,7 +8762,7 @@
         <v>45849.413194444001</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>5125</v>
       </c>
@@ -7625,7 +8785,7 @@
         <v>45849.420138889</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>5126</v>
       </c>
@@ -7648,7 +8808,7 @@
         <v>45849.425694443999</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>3769</v>
       </c>
@@ -7671,7 +8831,7 @@
         <v>45849.615972222004</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>3771</v>
       </c>
@@ -7694,7 +8854,7 @@
         <v>45849.649305555999</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>3772</v>
       </c>
@@ -7717,7 +8877,7 @@
         <v>45849.631944444001</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>3839</v>
       </c>
@@ -7740,7 +8900,7 @@
         <v>45849.625</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>3840</v>
       </c>
@@ -7763,7 +8923,7 @@
         <v>45849.642361111</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>3841</v>
       </c>
@@ -7786,7 +8946,7 @@
         <v>45849.658333332998</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>5167</v>
       </c>
@@ -7809,7 +8969,7 @@
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>5168</v>
       </c>
@@ -7832,7 +8992,7 @@
         <v>45849.652777777999</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>5169</v>
       </c>
@@ -7855,7 +9015,7 @@
         <v>45849.657638889003</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>5170</v>
       </c>
@@ -7878,7 +9038,7 @@
         <v>45849.663194444001</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>5171</v>
       </c>
@@ -7901,7 +9061,7 @@
         <v>45849.665277777996</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>5172</v>
       </c>
@@ -7924,7 +9084,7 @@
         <v>45849.670138889</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>5173</v>
       </c>
@@ -7947,7 +9107,7 @@
         <v>45849.675694443999</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>5174</v>
       </c>
@@ -7970,7 +9130,7 @@
         <v>45849.680555555999</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>5175</v>
       </c>
@@ -7993,7 +9153,7 @@
         <v>45849.683333333</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>5176</v>
       </c>
@@ -8016,7 +9176,7 @@
         <v>45849.684027777999</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>3751</v>
       </c>
@@ -8039,7 +9199,7 @@
         <v>45849.458333333001</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>3752</v>
       </c>
@@ -8062,7 +9222,7 @@
         <v>45849.482638889</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>3757</v>
       </c>
@@ -8085,7 +9245,7 @@
         <v>45849.497222222002</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>3833</v>
       </c>
@@ -8108,7 +9268,7 @@
         <v>45849.454861111</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>3834</v>
       </c>
@@ -8131,7 +9291,7 @@
         <v>45849.479166666999</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>3835</v>
       </c>
@@ -8154,7 +9314,7 @@
         <v>45849.503472222001</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>5157</v>
       </c>
@@ -8177,7 +9337,7 @@
         <v>45849.545138889</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>5158</v>
       </c>
@@ -8200,7 +9360,7 @@
         <v>45849.552083333001</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>5159</v>
       </c>
@@ -8223,7 +9383,7 @@
         <v>45849.555555555999</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>5160</v>
       </c>
@@ -8246,7 +9406,7 @@
         <v>45849.604166666999</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>5161</v>
       </c>
@@ -8269,7 +9429,7 @@
         <v>45849.611111111</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>5162</v>
       </c>
@@ -8292,7 +9452,7 @@
         <v>45849.618055555999</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>5163</v>
       </c>
@@ -8315,7 +9475,7 @@
         <v>45849.621527777999</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>5164</v>
       </c>
@@ -8338,7 +9498,7 @@
         <v>45849.628472222001</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>5165</v>
       </c>
@@ -8361,7 +9521,7 @@
         <v>45849.631944444001</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>5166</v>
       </c>
@@ -8384,7 +9544,7 @@
         <v>45849.635416666999</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>3758</v>
       </c>
@@ -8407,7 +9567,7 @@
         <v>45849.388888889</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>3759</v>
       </c>
@@ -8430,7 +9590,7 @@
         <v>45849.407638889003</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>3760</v>
       </c>
@@ -8453,7 +9613,7 @@
         <v>45849.421527778002</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>3836</v>
       </c>
@@ -8476,7 +9636,7 @@
         <v>45849.385416666999</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>3837</v>
       </c>
@@ -8499,7 +9659,7 @@
         <v>45849.402777777999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>3838</v>
       </c>
@@ -8522,7 +9682,7 @@
         <v>45849.414583332997</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>5127</v>
       </c>
@@ -8545,7 +9705,7 @@
         <v>45849.425694443999</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>5128</v>
       </c>
@@ -8568,7 +9728,7 @@
         <v>45849.429166667003</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>5129</v>
       </c>
@@ -8591,7 +9751,7 @@
         <v>45849.430555555999</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>5130</v>
       </c>
@@ -8614,7 +9774,7 @@
         <v>45849.4375</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>5131</v>
       </c>
@@ -8637,7 +9797,7 @@
         <v>45849.440972222001</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>5132</v>
       </c>
@@ -8660,7 +9820,7 @@
         <v>45849.447916666999</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>5133</v>
       </c>
@@ -8683,7 +9843,7 @@
         <v>45849.454861111</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>5134</v>
       </c>
@@ -8706,7 +9866,7 @@
         <v>45849.456944443999</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>5135</v>
       </c>
@@ -8729,7 +9889,7 @@
         <v>45849.461805555999</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>5137</v>
       </c>
@@ -8752,7 +9912,7 @@
         <v>45849.425694443999</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>3108</v>
       </c>
@@ -8775,7 +9935,7 @@
         <v>45761.40625</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>3109</v>
       </c>
@@ -8798,7 +9958,7 @@
         <v>45761.422916666997</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>3110</v>
       </c>
@@ -8821,7 +9981,7 @@
         <v>45761.449305556001</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>3126</v>
       </c>
@@ -8844,7 +10004,7 @@
         <v>45761.479166666999</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>3127</v>
       </c>
@@ -8867,7 +10027,7 @@
         <v>45761.486111111</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>3128</v>
       </c>
@@ -8890,7 +10050,7 @@
         <v>45761.493055555999</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>4283</v>
       </c>
@@ -8913,7 +10073,7 @@
         <v>45761.497916667002</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>4284</v>
       </c>
@@ -8936,7 +10096,7 @@
         <v>45761.503472222001</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>4285</v>
       </c>
@@ -8959,7 +10119,7 @@
         <v>45761.508333332997</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>4286</v>
       </c>
@@ -8982,7 +10142,7 @@
         <v>45761.513194444</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>4287</v>
       </c>
@@ -9005,7 +10165,7 @@
         <v>45761.517361111</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>4288</v>
       </c>
@@ -9028,7 +10188,7 @@
         <v>45761.522916667003</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>4289</v>
       </c>
@@ -9051,7 +10211,7 @@
         <v>45761.528472222002</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>4290</v>
       </c>
@@ -9074,7 +10234,7 @@
         <v>45761.534027777998</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>4291</v>
       </c>
@@ -9100,7 +10260,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>4292</v>
       </c>
@@ -9123,7 +10283,7 @@
         <v>45761.510416666999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>4293</v>
       </c>
@@ -9146,7 +10306,7 @@
         <v>45761.503472222001</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>4294</v>
       </c>
@@ -9169,7 +10329,7 @@
         <v>45761.541666666999</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>3763</v>
       </c>
@@ -9192,7 +10352,7 @@
         <v>45847.472222222001</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>3764</v>
       </c>
@@ -9215,7 +10375,7 @@
         <v>45847.477083332997</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>3765</v>
       </c>
@@ -9238,7 +10398,7 @@
         <v>45847.490972222004</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>3873</v>
       </c>
@@ -9261,7 +10421,7 @@
         <v>45847.381944444001</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>3874</v>
       </c>
@@ -9284,7 +10444,7 @@
         <v>45847.461805555999</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>3875</v>
       </c>
@@ -9307,7 +10467,7 @@
         <v>45847.479166666999</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>5084</v>
       </c>
@@ -9330,7 +10490,7 @@
         <v>45847.434027777999</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>5085</v>
       </c>
@@ -9353,7 +10513,7 @@
         <v>45847.458333333001</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>5086</v>
       </c>
@@ -9376,7 +10536,7 @@
         <v>45847.46875</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>5087</v>
       </c>
@@ -9399,7 +10559,7 @@
         <v>45847.4375</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>5088</v>
       </c>
@@ -9422,7 +10582,7 @@
         <v>45847.454861111</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>5089</v>
       </c>
@@ -9445,7 +10605,7 @@
         <v>45847.461805555999</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>5090</v>
       </c>
@@ -9468,7 +10628,7 @@
         <v>45847.472222222001</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>5091</v>
       </c>
@@ -9491,7 +10651,7 @@
         <v>45847.479166666999</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>5092</v>
       </c>
@@ -9514,7 +10674,7 @@
         <v>45847.486111111</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>5093</v>
       </c>
@@ -9537,7 +10697,7 @@
         <v>45847.496527777999</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>3123</v>
       </c>
@@ -9560,7 +10720,7 @@
         <v>45761.416666666999</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>3124</v>
       </c>
@@ -9583,7 +10743,7 @@
         <v>45761.433333333</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>3125</v>
       </c>
@@ -9606,7 +10766,7 @@
         <v>45761.444444444001</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>3317</v>
       </c>
@@ -9629,7 +10789,7 @@
         <v>45761.395833333001</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>3318</v>
       </c>
@@ -9652,7 +10812,7 @@
         <v>45761.427083333001</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>3319</v>
       </c>
@@ -9675,7 +10835,7 @@
         <v>45761.46875</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>4275</v>
       </c>
@@ -9698,7 +10858,7 @@
         <v>45761.416666666999</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>4276</v>
       </c>
@@ -9721,7 +10881,7 @@
         <v>45761.419444444</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>4277</v>
       </c>
@@ -9744,7 +10904,7 @@
         <v>45761.427777778001</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>4278</v>
       </c>
@@ -9767,7 +10927,7 @@
         <v>45396.434027777999</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>4279</v>
       </c>
@@ -9790,7 +10950,7 @@
         <v>45761.439583332998</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>4280</v>
       </c>
@@ -9813,7 +10973,7 @@
         <v>45761.444444444001</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>4281</v>
       </c>
@@ -9836,7 +10996,7 @@
         <v>45761.45</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>4282</v>
       </c>
@@ -9859,7 +11019,7 @@
         <v>45761.456250000003</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>4295</v>
       </c>
@@ -9882,7 +11042,7 @@
         <v>45761.423611111</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>4296</v>
       </c>
@@ -9905,7 +11065,7 @@
         <v>45761.434027777999</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>4297</v>
       </c>
@@ -9928,7 +11088,7 @@
         <v>45761.451388889</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>4298</v>
       </c>
@@ -9951,7 +11111,7 @@
         <v>45761.46875</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>3761</v>
       </c>
@@ -9974,7 +11134,7 @@
         <v>45847.375</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>3762</v>
       </c>
@@ -9997,7 +11157,7 @@
         <v>45847.404861110997</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>3953</v>
       </c>
@@ -10020,7 +11180,7 @@
         <v>45847.381944444001</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>3954</v>
       </c>
@@ -10043,7 +11203,7 @@
         <v>45847.400694443997</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>3955</v>
       </c>
@@ -10066,7 +11226,7 @@
         <v>45847.421527778002</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>5072</v>
       </c>
@@ -10089,7 +11249,7 @@
         <v>45847.371527777999</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>5073</v>
       </c>
@@ -10112,7 +11272,7 @@
         <v>45847.375</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>5074</v>
       </c>
@@ -10135,7 +11295,7 @@
         <v>45847.378472222001</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>5075</v>
       </c>
@@ -10158,7 +11318,7 @@
         <v>45847.388888889</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>5076</v>
       </c>
@@ -10181,7 +11341,7 @@
         <v>45847.391666666997</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>5077</v>
       </c>
@@ -10204,7 +11364,7 @@
         <v>45847.393055556</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>5080</v>
       </c>
@@ -10227,7 +11387,7 @@
         <v>45847.402777777999</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>5081</v>
       </c>
@@ -10250,7 +11410,7 @@
         <v>45847.414583332997</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>5082</v>
       </c>
@@ -10273,7 +11433,7 @@
         <v>45847.430555555999</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>5083</v>
       </c>
@@ -10296,7 +11456,7 @@
         <v>45847.430555555999</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>3161</v>
       </c>
@@ -10319,7 +11479,7 @@
         <v>45764.416666666999</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>3162</v>
       </c>
@@ -10342,7 +11502,7 @@
         <v>45764.4375</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>3167</v>
       </c>
@@ -10365,7 +11525,7 @@
         <v>45764.447916666999</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>3296</v>
       </c>
@@ -10388,7 +11548,7 @@
         <v>45764.395833333001</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>3297</v>
       </c>
@@ -10411,7 +11571,7 @@
         <v>45764.430555555999</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>3309</v>
       </c>
@@ -10434,7 +11594,7 @@
         <v>45764.46875</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>4347</v>
       </c>
@@ -10457,7 +11617,7 @@
         <v>45764.419444444</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>4348</v>
       </c>
@@ -10480,7 +11640,7 @@
         <v>45764.422916666997</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>4349</v>
       </c>
@@ -10503,7 +11663,7 @@
         <v>45764.426388888998</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>4350</v>
       </c>
@@ -10526,7 +11686,7 @@
         <v>45764.431250000001</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>4351</v>
       </c>
@@ -10549,7 +11709,7 @@
         <v>45764.434722222002</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>4352</v>
       </c>
@@ -10572,7 +11732,7 @@
         <v>45764.438194444003</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>4353</v>
       </c>
@@ -10595,7 +11755,7 @@
         <v>45764.442361111003</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>4354</v>
       </c>
@@ -10618,7 +11778,7 @@
         <v>45764.446527777996</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>4355</v>
       </c>
@@ -10641,7 +11801,7 @@
         <v>45764.430555555999</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>4356</v>
       </c>
@@ -10664,7 +11824,7 @@
         <v>45764.4375</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>4357</v>
       </c>
@@ -10687,7 +11847,7 @@
         <v>45764.444444444001</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>4358</v>
       </c>
@@ -10710,7 +11870,7 @@
         <v>45764.454861111</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>3170</v>
       </c>
@@ -10733,7 +11893,7 @@
         <v>45764.475694444001</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>3171</v>
       </c>
@@ -10756,7 +11916,7 @@
         <v>45764.494444443997</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>3172</v>
       </c>
@@ -10779,7 +11939,7 @@
         <v>45764.494444443997</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>3293</v>
       </c>
@@ -10802,7 +11962,7 @@
         <v>45764.40625</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>3294</v>
       </c>
@@ -10825,7 +11985,7 @@
         <v>45764.419444444</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>3295</v>
       </c>
@@ -10848,7 +12008,7 @@
         <v>45764.442361111003</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>4359</v>
       </c>
@@ -10871,7 +12031,7 @@
         <v>45764.501388889003</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>4360</v>
       </c>
@@ -10894,7 +12054,7 @@
         <v>45764.505555556003</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>4361</v>
       </c>
@@ -10917,7 +12077,7 @@
         <v>45764.510416666999</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>4362</v>
       </c>
@@ -10940,7 +12100,7 @@
         <v>45764.513888889</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>4363</v>
       </c>
@@ -10963,7 +12123,7 @@
         <v>45764.527777777999</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>4364</v>
       </c>
@@ -10986,7 +12146,7 @@
         <v>45764.534027777998</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>4365</v>
       </c>
@@ -11009,7 +12169,7 @@
         <v>45764.538194444001</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>4366</v>
       </c>
@@ -11032,7 +12192,7 @@
         <v>45764.541666666999</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>4367</v>
       </c>
@@ -11055,7 +12215,7 @@
         <v>45765.472222222001</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>4368</v>
       </c>
@@ -11078,7 +12238,7 @@
         <v>45765.476388889001</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>4369</v>
       </c>
@@ -11101,7 +12261,7 @@
         <v>45765.481944444</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>4370</v>
       </c>
@@ -11133,14 +12293,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -11151,7 +12311,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11162,7 +12322,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -11173,7 +12333,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5</v>
       </c>
@@ -11184,7 +12344,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>8</v>
       </c>
@@ -11195,7 +12355,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7</v>
       </c>
@@ -11206,7 +12366,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10</v>
       </c>
@@ -11217,7 +12377,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>9</v>
       </c>
@@ -11228,7 +12388,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>12</v>
       </c>
@@ -11239,7 +12399,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>14</v>
       </c>
@@ -11250,7 +12410,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>15</v>
       </c>
@@ -11261,7 +12421,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>16</v>
       </c>
@@ -11272,7 +12432,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>17</v>
       </c>
@@ -11283,7 +12443,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>18</v>
       </c>
@@ -11303,7 +12463,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
@@ -11312,7 +12472,7 @@
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -11329,7 +12489,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
@@ -11340,7 +12500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>5</v>
       </c>
@@ -11351,7 +12511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>6</v>
       </c>
@@ -11362,7 +12522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>7</v>
       </c>
@@ -11376,7 +12536,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>8</v>
       </c>
@@ -11387,7 +12547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>12</v>
       </c>
@@ -11398,7 +12558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>13</v>
       </c>
@@ -11409,7 +12569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>14</v>
       </c>
@@ -11420,7 +12580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>15</v>
       </c>
@@ -11431,7 +12591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>17</v>
       </c>
@@ -11442,7 +12602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20</v>
       </c>
@@ -11453,7 +12613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>21</v>
       </c>
@@ -11464,7 +12624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>24</v>
       </c>
@@ -11475,7 +12635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>25</v>
       </c>
@@ -11486,7 +12646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>29</v>
       </c>
@@ -11497,7 +12657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>31</v>
       </c>
@@ -11508,7 +12668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>32</v>
       </c>
@@ -11519,7 +12679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>33</v>
       </c>
@@ -11530,7 +12690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>45</v>
       </c>
@@ -11541,7 +12701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>46</v>
       </c>
@@ -11552,7 +12712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>50</v>
       </c>
@@ -11563,7 +12723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>51</v>
       </c>
@@ -11574,7 +12734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>60</v>
       </c>
@@ -11585,7 +12745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>66</v>
       </c>
@@ -11596,7 +12756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>70</v>
       </c>
@@ -11607,7 +12767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>71</v>
       </c>
@@ -11618,7 +12778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>72</v>
       </c>
@@ -11629,7 +12789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>77</v>
       </c>
@@ -11640,7 +12800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>78</v>
       </c>
@@ -11651,7 +12811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>81</v>
       </c>
@@ -11662,7 +12822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>82</v>
       </c>
@@ -11673,7 +12833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>84</v>
       </c>
@@ -11684,7 +12844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>99</v>
       </c>
@@ -11698,7 +12858,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>117</v>
       </c>
@@ -11712,7 +12872,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>127</v>
       </c>
@@ -11723,7 +12883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>128</v>
       </c>
@@ -11734,7 +12894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>130</v>
       </c>
@@ -11745,7 +12905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>133</v>
       </c>
@@ -11756,7 +12916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>134</v>
       </c>
@@ -11767,7 +12927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>135</v>
       </c>
@@ -11778,7 +12938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>136</v>
       </c>
@@ -11789,7 +12949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>155</v>
       </c>
@@ -11803,7 +12963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>164</v>
       </c>
@@ -11817,7 +12977,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>165</v>
       </c>
@@ -11831,7 +12991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>173</v>
       </c>
@@ -11845,7 +13005,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>177</v>
       </c>
@@ -11859,7 +13019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>178</v>
       </c>
@@ -11873,7 +13033,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>189</v>
       </c>
@@ -11887,7 +13047,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>192</v>
       </c>
@@ -11901,7 +13061,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>200</v>
       </c>
@@ -11915,7 +13075,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>206</v>
       </c>
@@ -11929,7 +13089,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>207</v>
       </c>
@@ -11943,7 +13103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>214</v>
       </c>
@@ -11957,7 +13117,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>266</v>
       </c>
@@ -11974,7 +13134,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>269</v>
       </c>
@@ -11991,7 +13151,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>277</v>
       </c>
@@ -12008,7 +13168,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>283</v>
       </c>
@@ -12025,7 +13185,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>284</v>
       </c>
@@ -12042,7 +13202,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>360</v>
       </c>
@@ -12068,7 +13228,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
@@ -12076,7 +13236,7 @@
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -12093,7 +13253,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>18</v>
       </c>
@@ -12110,7 +13270,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>27</v>
       </c>
@@ -12127,7 +13287,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>28</v>
       </c>
@@ -12144,7 +13304,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>36</v>
       </c>
@@ -12161,7 +13321,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>40</v>
       </c>
@@ -12175,7 +13335,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>41</v>
       </c>
@@ -12192,7 +13352,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>52</v>
       </c>
@@ -12209,7 +13369,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>55</v>
       </c>
@@ -12226,7 +13386,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>63</v>
       </c>
@@ -12243,7 +13403,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>69</v>
       </c>
@@ -12260,7 +13420,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>70</v>
       </c>
@@ -12277,7 +13437,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>76</v>
       </c>
@@ -12294,7 +13454,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>99</v>
       </c>
@@ -12317,7 +13477,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
@@ -12326,15 +13486,15 @@
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.28515625" customWidth="1"/>
+    <col min="9" max="9" width="2.26953125" customWidth="1"/>
     <col min="10" max="10" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.28515625" customWidth="1"/>
+    <col min="13" max="13" width="2.26953125" customWidth="1"/>
     <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12352,7 +13512,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -12392,7 +13552,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -12427,7 +13587,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -12462,7 +13622,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -12497,7 +13657,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -12532,7 +13692,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -12567,7 +13727,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>8</v>
       </c>
@@ -12602,7 +13762,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>10</v>
       </c>
@@ -12637,7 +13797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>12</v>
       </c>
@@ -12672,7 +13832,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>13</v>
       </c>
@@ -12707,7 +13867,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>15</v>
       </c>
@@ -12742,7 +13902,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>17</v>
       </c>
@@ -12777,7 +13937,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>18</v>
       </c>
@@ -12812,7 +13972,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>19</v>
       </c>
@@ -12847,7 +14007,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20</v>
       </c>
@@ -12882,7 +14042,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>23</v>
       </c>
@@ -12917,7 +14077,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>35</v>
       </c>
@@ -12952,7 +14112,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>36</v>
       </c>
@@ -12987,7 +14147,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>37</v>
       </c>
@@ -13022,7 +14182,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>38</v>
       </c>
@@ -13057,7 +14217,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>42</v>
       </c>
@@ -13092,7 +14252,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>43</v>
       </c>
@@ -13127,7 +14287,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>46</v>
       </c>
@@ -13159,7 +14319,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>47</v>
       </c>
@@ -13194,7 +14354,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>48</v>
       </c>
@@ -13229,7 +14389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>49</v>
       </c>
@@ -13264,7 +14424,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>50</v>
       </c>
@@ -13299,7 +14459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>52</v>
       </c>
@@ -13334,7 +14494,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>53</v>
       </c>
@@ -13369,7 +14529,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>56</v>
       </c>
@@ -13404,7 +14564,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>58</v>
       </c>
@@ -13439,7 +14599,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>59</v>
       </c>
@@ -13474,7 +14634,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>60</v>
       </c>
@@ -13509,7 +14669,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>61</v>
       </c>
@@ -13544,7 +14704,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>62</v>
       </c>
@@ -13579,7 +14739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>63</v>
       </c>
@@ -13614,7 +14774,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>66</v>
       </c>
@@ -13649,7 +14809,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>67</v>
       </c>
@@ -13684,7 +14844,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>68</v>
       </c>
@@ -13719,7 +14879,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>72</v>
       </c>
@@ -13754,7 +14914,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>75</v>
       </c>
@@ -13789,7 +14949,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>76</v>
       </c>
@@ -13824,7 +14984,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>81</v>
       </c>
@@ -13862,7 +15022,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>82</v>
       </c>
@@ -13900,7 +15060,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>83</v>
       </c>
@@ -13938,7 +15098,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>84</v>
       </c>
@@ -13976,7 +15136,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>86</v>
       </c>
@@ -14014,7 +15174,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>87</v>
       </c>
@@ -14052,7 +15212,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>89</v>
       </c>
@@ -14090,7 +15250,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>90</v>
       </c>
@@ -14128,7 +15288,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>91</v>
       </c>
@@ -14163,7 +15323,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>93</v>
       </c>
@@ -14198,7 +15358,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>95</v>
       </c>
@@ -14233,7 +15393,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>96</v>
       </c>
@@ -14268,7 +15428,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>101</v>
       </c>
@@ -14297,7 +15457,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>114</v>
       </c>
@@ -14329,7 +15489,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>122</v>
       </c>
@@ -14367,7 +15527,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>123</v>
       </c>
@@ -14405,7 +15565,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>124</v>
       </c>
@@ -14443,7 +15603,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>126</v>
       </c>
@@ -14481,7 +15641,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>127</v>
       </c>
@@ -14519,7 +15679,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>129</v>
       </c>
@@ -14557,7 +15717,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>130</v>
       </c>
